--- a/ksoft_old/docs/records/Itinerarios_CD2567_Records.xlsx
+++ b/ksoft_old/docs/records/Itinerarios_CD2567_Records.xlsx
@@ -3030,13 +3030,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26BCF318-9A15-4CBD-BFCA-AD7D109B5533}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F2BD569-5A2F-406E-A008-36690604E37B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B849B6B1-0DC4-4EDC-B929-D9FB45C5B9E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3ACE1768-C3CA-469F-B006-33A414FD286D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE3B23E0-B4B1-4BAF-B469-FA487201F103}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94A70B52-586B-4E8B-87B0-83C22FB10F26}"/>
 </file>
--- a/ksoft_old/docs/records/Itinerarios_CD2567_Records.xlsx
+++ b/ksoft_old/docs/records/Itinerarios_CD2567_Records.xlsx
@@ -3030,13 +3030,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F2BD569-5A2F-406E-A008-36690604E37B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE7091CD-FA37-4E03-8459-1FB7DDB31AA0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3ACE1768-C3CA-469F-B006-33A414FD286D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E7B6EE7-E668-40B8-B70F-AA4CD207BEF1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94A70B52-586B-4E8B-87B0-83C22FB10F26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{896F889F-5332-479B-9D6B-D58A4A2984EE}"/>
 </file>
--- a/ksoft_old/docs/records/Itinerarios_CD2567_Records.xlsx
+++ b/ksoft_old/docs/records/Itinerarios_CD2567_Records.xlsx
@@ -3030,13 +3030,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE7091CD-FA37-4E03-8459-1FB7DDB31AA0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26BCF318-9A15-4CBD-BFCA-AD7D109B5533}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E7B6EE7-E668-40B8-B70F-AA4CD207BEF1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B849B6B1-0DC4-4EDC-B929-D9FB45C5B9E4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{896F889F-5332-479B-9D6B-D58A4A2984EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE3B23E0-B4B1-4BAF-B469-FA487201F103}"/>
 </file>